--- a/AAII_Financials/Quarterly/ELUXY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ELUXY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="92">
   <si>
     <t>ELUXY</t>
   </si>
@@ -656,177 +656,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -869,86 +873,89 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3">
         <v>3503600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3401400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3265200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2843700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3231000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2931500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2823900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2744700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3202400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3154600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2411200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2933700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>13528100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3672700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3377500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3227600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>13254000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3200300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3258500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2900300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3506900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3126100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3331200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3201400</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>3649000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>3502300</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,86 +998,89 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>3169900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2971200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2815600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2353600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2663000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2405600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2260800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2160800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2473200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2442700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2067000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2494600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>11056600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3079700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2742900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2639100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>10958100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2589400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2642300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2391900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2780200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2466100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2603800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2530600</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2904700</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>2753100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1113,86 +1123,89 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3">
         <v>333700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>430200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>449600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>490100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>568000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>525800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>563100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>583900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>729100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>712000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>344200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>439100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2471500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>593000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>634500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>588400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2295900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>610900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>616200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>508300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>726700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>659900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>727400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>670800</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>744200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>749200</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,8 +1496,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1526,20 +1546,20 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>33800</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-61900</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1547,8 +1567,8 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1560,20 +1580,20 @@
         <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>220400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>35100</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>124100</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1583,8 +1603,8 @@
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL14" s="3">
         <v>0</v>
@@ -1601,8 +1621,11 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1645,8 +1668,8 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,8 +1790,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1808,86 +1835,89 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3">
         <v>3695900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3438600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3211000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2695000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3150400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2776100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2639100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2527500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2966400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2837200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2417600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2920200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13165600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3543900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3236600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3233800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>12774600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3015700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3172600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2820900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3284600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2912800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3124700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3037700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3465500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3295000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1930,86 +1960,89 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3">
         <v>-192400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-37200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>54200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>148700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>80600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>155300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>184800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>217200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>236000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>317400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>13500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>362600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>128700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>140800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-6200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>479400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>184600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>86000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>79400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>222300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>213200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>206600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>163700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>183400</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>207300</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,8 +2085,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2096,86 +2130,89 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>-50000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-38700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-28500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-23800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-16600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-11900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-11000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-16200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-19400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-18800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-83300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-21200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-20600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-18400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-48400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-12800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-8200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-6900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-9300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-20300</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-11600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-42100</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2218,86 +2255,89 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>-103100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>60100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>154100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>241200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>166000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>256700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>274900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>309100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>326500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>409200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>94100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>128000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>827400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>261300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>255700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>112600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>907300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>277800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>187100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>174400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>324400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>308800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>293200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>265200</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>260000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>309600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2340,8 +2380,8 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2418,8 +2458,11 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2462,86 +2505,89 @@
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3">
         <v>-242300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-75900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>25600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>124900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>63900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>143400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>173800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>205900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>220900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>301200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-25800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>279200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>107500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>120300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-24600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>430900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>171800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>77700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>69800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>215400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>204000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>186200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>152100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>141300</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>195800</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2584,86 +2630,89 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3">
         <v>-54200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-17500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>35200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>9500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>35100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>45000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>58600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>45300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>69000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>72300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>33500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-5400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>103300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>49600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>24000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>12600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>49000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>47300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>37200</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-3100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>52000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,8 +2833,11 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2828,86 +2880,89 @@
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3">
         <v>-188200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-58400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>24800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>89700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>54400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>108300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>128800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>147200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>175600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>232200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-14600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-9500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>206900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>74000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>116200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-19200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>327600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>122100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>53700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>57300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>215500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>155000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>139000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>114900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>144400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>143800</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2950,86 +3005,89 @@
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3">
         <v>-188300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-58400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>24900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>89700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>54400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>108300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>128800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>147100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>175700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>232200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-14500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-9500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>207000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>73900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>116200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-19200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>327600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>122100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>53900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>57300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>215500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>155000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>139000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>114900</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>144500</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>143800</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3194,8 +3255,8 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -3228,38 +3289,38 @@
         <v>0</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>286400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>78200</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>15500</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>14600</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>28500</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>109200</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-13800</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,8 +3583,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3560,86 +3630,89 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>50000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>38700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>28500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>23800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>16600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>11900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>11000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>11300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>15000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>16200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>19400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>18800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>83300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>21200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>20600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>18400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>48400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>12800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>9600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>6900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>9300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>20300</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>11600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>42100</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3682,86 +3755,89 @@
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3">
         <v>-188300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-58400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>24900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>89700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>54400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>108300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>128800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>147100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>175700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>232200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-14500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>276900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>285300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>89400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>130800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>9300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>436800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>122100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>53900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>57300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>201700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>155000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>139000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>114900</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>144500</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>143800</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,8 +3958,11 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3926,213 +4005,219 @@
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3">
         <v>-188300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-58400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>24900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>89700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>54400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>108300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>128800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>147100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>175700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>232200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-14500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>276900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>285300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>89400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>130800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>9300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>436800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>122100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>53900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>57300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>201700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>155000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>139000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>114900</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>144500</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>143800</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,1106 +4305,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1734200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1074100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1698800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1273000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1106200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1232400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1461100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1595700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1417500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1307000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1524500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1495400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1162800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1115500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1719900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>907500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1178900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>752100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>997700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1703500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1689800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1808100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1907700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1918200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1720100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1541000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1228800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1165000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>889900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1033100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1342700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1143100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>956900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>859700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1215100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1193100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1084900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>855300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1448100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1275500</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>364600</v>
+      </c>
+      <c r="E42" s="3">
         <v>17800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>17700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>17400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>17200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>16400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>15200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>16400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>15900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>15800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>16600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>15600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>15800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>16200</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>16500</v>
       </c>
       <c r="R42" s="3">
         <v>16500</v>
       </c>
       <c r="S42" s="3">
+        <v>16500</v>
+      </c>
+      <c r="T42" s="3">
         <v>16400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>15700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>15100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>15500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>15200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>15400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>16200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>17300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>18200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>19600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>21600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>23400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>20800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>63400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>20200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>18700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>12100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>17000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>38500</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>17200</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>16500</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>24000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>102700</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2502500</v>
+      </c>
+      <c r="E43" s="3">
         <v>2462000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2787200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2363800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2296900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2164600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2578700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2300100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2220100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2211200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2622800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2170900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2260600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2296200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2223000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2328700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2278200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2149100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2198500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2070600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1995900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2070500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1968400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1954700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1705700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2085200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2474100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2671400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2662300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2613700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2550600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2125200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2184900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2168400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2322500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2107400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2053800</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2203200</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>2282800</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>2166100</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2346400</v>
+      </c>
+      <c r="E44" s="3">
         <v>2335100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2167600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2475600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2432100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2220900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1922000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2221600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2000900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2004600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1985200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2222000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2320900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2365600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2387400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3020800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2872200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2489300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1870500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2022300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1791800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1630400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1248100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1380600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1470300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1861000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1841300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2426000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2217700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2241200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1922700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1933700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1837400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1745200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1577500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1765200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1648000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1816200</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1523200</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1734500</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>689000</v>
+      </c>
+      <c r="E45" s="3">
         <v>626600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>29700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>595400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>557800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>527000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>79100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>485800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>471700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>486200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>535800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>552600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>554900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>509100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>594600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>565400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>550800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>441700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>418900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>402700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>434400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>376000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>377900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>436000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>596400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1443000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>680600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>560800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>534300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>533400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>440700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>490700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>476200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>422700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>602900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>552600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>550300</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>530300</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>562200</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7636700</v>
+      </c>
+      <c r="E46" s="3">
         <v>6515600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6851300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6725200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6410200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6161400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6196900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6619500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6126000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6025000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6299700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6439700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6312700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6348400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6855900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6868000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6911000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5956900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5523400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6230800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5895400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5958800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5516400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5648800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5350300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6103200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7008700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6966400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6351500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6485600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6369700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5661300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5481900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5266500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>5576400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5685800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>5355700</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>5449000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>5887000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>5738500</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E47" s="3">
         <v>7300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7400</v>
-      </c>
-      <c r="F47" s="3">
-        <v>7300</v>
       </c>
       <c r="G47" s="3">
         <v>7300</v>
       </c>
       <c r="H47" s="3">
+        <v>7300</v>
+      </c>
+      <c r="I47" s="3">
         <v>6900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>26800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>26700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>28200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>26200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>26500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>27500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>27700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>32600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>32300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>32700</v>
-      </c>
-      <c r="W47" s="3">
-        <v>33100</v>
       </c>
       <c r="X47" s="3">
         <v>33100</v>
       </c>
       <c r="Y47" s="3">
+        <v>33100</v>
+      </c>
+      <c r="Z47" s="3">
         <v>32000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>40000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>48400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>53900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>58800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>87500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>79500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>82500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>73800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>65700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>60900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>61600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>59100</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>43800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>44200</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>57600</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>56400</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>55900</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2801300</v>
+      </c>
+      <c r="E48" s="3">
         <v>2988300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3087500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3126600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3157800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3062800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2996100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3143400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3089700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3153000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3288100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3159600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3285600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3233300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3308900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3242500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3040200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2780800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2575100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2292500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2182600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2210000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2154000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2296600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2452500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2795400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2798600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3056600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2837100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2855600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2420700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2083500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2047500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2012900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2065800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1953900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1948800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2135000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2125700</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2119000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>967500</v>
+      </c>
+      <c r="E49" s="3">
         <v>989300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1018600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1016600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1021600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>986300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>962700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1131900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1146000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1137800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>976300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1165900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1193200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1189400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1205200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1201800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1148300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1067300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>976400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>982000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>955200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>972500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>930300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1005500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1054500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1178300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1238000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1627700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1528800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1477300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1395600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1232800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1246400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1234500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1223800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1178300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1212700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1186600</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>891600</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>964900</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>547400</v>
+      </c>
+      <c r="E52" s="3">
         <v>488900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>521000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>461100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>407100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>400600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>348500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>426700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>373300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>349700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>310600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>264300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>244100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>284100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1051900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1033300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>999100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>845200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>741000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>802400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>773700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>771500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>775900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>871900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>980700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1090000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1040000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1127700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>979700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>993700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>910600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>760300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>740500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>695900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>713200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>674700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>684700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>768200</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>784800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>796300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13057500</v>
+      </c>
+      <c r="E54" s="3">
         <v>12085200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12436000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12310400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11947800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11520800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11329600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12286100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11637700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11527200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11937600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11846400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11846200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11850700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>12449600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>12378400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12131000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10664000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9828800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10340500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>9839900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9945900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9408600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9862700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>9886400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11220800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12144100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12865900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11776500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>11894700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>11170400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9803700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>9577300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>9271500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>9638300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>9536500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>9246200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>9596300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>9745500</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>9674600</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3740000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3719900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3827500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3801200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3803500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3716600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3705400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3707200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3521700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3504000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3619700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3397500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3505900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3478300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3757100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4264600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4110900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3709600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3487500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3355400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3274800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3361700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2957200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2832000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2612900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3595600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3853500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4213000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3960400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4070100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3953700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3386500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3363700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3215300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3349100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3250700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3161400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3300400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>3210700</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>3144700</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1458100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1274800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1103500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>678600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>755000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>735000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>766600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>953200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>917500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>798100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>878200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>807400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>901000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1048900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>923800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1062000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1007900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>678900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>588700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>579600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>540800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>438100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>199600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>312700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>605100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>528100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>474200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>566300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>587500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>706700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>453700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>299200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>286600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>224600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>290100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>302900</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>285900</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>311600</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>205100</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>183600</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2145100</v>
+      </c>
+      <c r="E59" s="3">
         <v>1972100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1332000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2203100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2128100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2069400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1395600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2408000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2200100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2198200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1590500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2106100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2150300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2089800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2312800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2406900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2386300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2353800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2212900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2759800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2121000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2165100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1938700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2038100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1958200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1994100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2791800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2667900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2307000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2158200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2350300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2203000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2097900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1781800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2055300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2209700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2047400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2114300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2177500</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>2120100</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7343200</v>
+      </c>
+      <c r="E60" s="3">
         <v>6966800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7121400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6682800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6686700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6521000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6666800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7068500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6639300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6500300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6855100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6310900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6557200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6617000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6993600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7733400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7505200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6742200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6289100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6694800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5936600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5964900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5095500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5182800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5176200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6117800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7119600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7447200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6854900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6935000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6757700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5888700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5748300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5221700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5694500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>5763400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>5494700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>5726300</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>5593400</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>5448400</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3171400</v>
+      </c>
+      <c r="E61" s="3">
         <v>3411600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3646000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3997000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3727800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3554300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3189000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3521000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3309200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3298500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3211200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3328700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2985700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3000000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3129300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2021900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1913000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1535500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1130600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1132200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1096500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1259600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1507300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1619800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1711900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1684000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1201700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1210700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1145300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1041100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>711500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>767500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>772800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>792200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>709000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>744200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>799200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>788600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>902700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>958600</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>500200</v>
+      </c>
+      <c r="E62" s="3">
         <v>465700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>442900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>445200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>426200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>387400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>358400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>530700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>490500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>469900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>476000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>452500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>461300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>467900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>715500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>677200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>719100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>698100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>709300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>854500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>809200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>857200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1038600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1101800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1244000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1383400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1256200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1618700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1336300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1236400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1204700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>973000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>968200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>997400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1030300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1072100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1108000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1207500</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1235800</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1480400</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11260200</v>
+      </c>
+      <c r="E66" s="3">
         <v>11102300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11491500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11406300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11096400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10691700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10451000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11400300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10675200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10499800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10816600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10314400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10253200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10310200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10839100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10433200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10138000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8976500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8129500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8682200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7843000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8082400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7642000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7905100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8132800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9185900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9578300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>10277800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9337700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>9213700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>8675100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7630500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7490700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7012700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>7435300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>7582100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>7405000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>7725800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>7735300</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>7890800</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1292900</v>
+      </c>
+      <c r="E72" s="3">
         <v>846900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>903500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>797900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>742300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>716700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>618600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>639800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>675300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>641700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>774000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1095200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1085400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1178100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1174700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1515800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1562500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1267500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1292800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1236500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1582400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1442700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1346300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1519100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1296500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1543700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2059900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2049400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1924800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2157000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1984600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1705600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1624100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1796300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1723900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1475400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1362100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1365300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1505000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1278700</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1796800</v>
+      </c>
+      <c r="E76" s="3">
         <v>982400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>943900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>903600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>850800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>828700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>878100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>885300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>962000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1026900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1120400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1531400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1592400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1539800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1610500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1945200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1993000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1687500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1699300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1658300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1997000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1863500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1766600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1957600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1753600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2034900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2565800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2588200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2438800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2681000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2495300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2173300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2086600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2258800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2203000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1954400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1841200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1870500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>2010200</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>1783900</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,135 +8688,141 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8670,86 +8865,89 @@
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3">
         <v>-188300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-58400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>24900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>89700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>54400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>108300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>128800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>147100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>175700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>232200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-14500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>276900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>285300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>89400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>130800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>9300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>436800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>122100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>53900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>57300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>201700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>155000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>139000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>114900</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>144500</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>143800</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>147500</v>
+      </c>
+      <c r="E83" s="3">
         <v>146000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>30400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>157100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>151100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>148200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>43000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>146500</v>
       </c>
       <c r="K83" s="3">
         <v>146500</v>
       </c>
       <c r="L83" s="3">
+        <v>146500</v>
+      </c>
+      <c r="M83" s="3">
         <v>144900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>48800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>126900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>129600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>131900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>139200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>136000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>128500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>116300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>102000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>113300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>101100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>103300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>105500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>107900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>119900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>133300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>580300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>161800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>142800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>144300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>476400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>106100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>109300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>104600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>109000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>104800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>107000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>113100</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>118600</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>160500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-507300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>498600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>77200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-118900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-300400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>292700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>177300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>131300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-208800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>383700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>105100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>328600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-439000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>145300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-47900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>120600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-425600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>325700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>115000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>192300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>20500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>624100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>651400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>94100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-180300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>958900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>497100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>164400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-251700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>923600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>280500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>289700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-233500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>395600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>325700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>423700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-69600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>343400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>390300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-49300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-33600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-73900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-61400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-54500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-53100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-120900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-71300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-68500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-61800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-155800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-84000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-78200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-71400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2446000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1906000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1699000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1339000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2284000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1292000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-92100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-56800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-163500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-81000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-85100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-104100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-604900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-160900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-101400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-92700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-533800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-119300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-82500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-63900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-182000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-102500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-70800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-83100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-145000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-90700</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-55900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-48300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-81700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-90100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-49400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-61100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-58900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-129500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-118300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-99000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-128600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-60900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-120400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-106500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-194800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-205700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-145000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-126800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-284300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-157800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-122500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-68400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-186500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-99000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-105100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-123000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-795200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-225700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-162900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-149700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-746800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-138300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-131900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-119700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-227100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-139400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-186100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-348100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-81800</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-100200</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,8 +10455,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10266,36 +10500,36 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3">
         <v>-121700</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-123700</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-104900</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-107200</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-190100</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -10303,49 +10537,52 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-277800</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-141100</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-273800</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-124000</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-115900</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
         <v>0</v>
       </c>
       <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-122400</v>
       </c>
-      <c r="AO96" s="3">
-        <v>0</v>
-      </c>
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>551900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-38200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>13000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>173100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-18400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>37900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-238400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>81200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>91200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>197700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-314700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>306800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-134300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-26800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>872100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-12200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>393100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>260600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-694200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>26900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-157200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-73900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-352200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-277600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>325800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>595600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-116900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-45500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-77300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>47500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-142900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>46500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-68600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>20800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-150300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-84100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>57600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-174400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-63900</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-55200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-14800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-16700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-36400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-6600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>18300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-7900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-23200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>39900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>14200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-23700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>39600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>12600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>8700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-4500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>20000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-15800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-28700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-16100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>19600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>17800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>6800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>16600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>13000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-13400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>18900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>3900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>5900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-21200</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-25100</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>679500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-571100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>397400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>156700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-194800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-378800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>114300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>99100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-126800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-96000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>344300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>92100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-580300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>798900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-268500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>408300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-279300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-644000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-15200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-92000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-101700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>69600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>267400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>286200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>276300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-27200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>232400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-123700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-344300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>46800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>175200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>97200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-313600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>22100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>108200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>273900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-592800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>172600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>306300</v>
       </c>
     </row>
